--- a/review-tasks/1b-testcase-review/jury/fixed/testcases.xlsx
+++ b/review-tasks/1b-testcase-review/jury/fixed/testcases.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q251"/>
+  <dimension ref="A1:Q248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Сообщение о минимальной сумме не выводится, кнопка «Далее» активна</t>
+          <t>Под полем «Сумма» сообщение о минимальной сумме не выводится</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Сообщение о минимальной сумме больше не выводится, кнопка «Далее» активна</t>
+          <t>Сообщение о минимальной сумме под полем «Сумма» больше не выводится</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Сообщение о минимальной сумме не выводится, кнопка «Далее» активна</t>
+          <t>Под полем «Сумма» сообщение о минимальной сумме не выводится</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562</t>
+          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562, остаток 5 000,00 ₽</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Остаток счёта увеличился на 100 000,82 ₽</t>
+          <t>Остаток счёта — 105 000,82 ₽</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Клиенту меньше 18 лет. Операция проводится с участием законного представителя.», отображается блок «Законный представитель», кнопка «Далее» неактивна</t>
+          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Клиенту меньше 18 лет. Операция проводится с участием законного представителя.», отображается блок «Законный представитель», кнопка «Далее» неактивна. Запомнить значение поля «Сумма к выплате»</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», сумма к выплате зачислена на счёт 40817810700000045672</t>
+          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», сумма из поля «Сумма к выплате» (шаг 2) зачислена на счёт 40817810700000045672</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Закрытие вклада в день 18-летия клиента: без законного представителя, электронное подписание</t>
+          <t>Закрытие вклада в день 18-летия клиента: без законного представителя, электронное подписание со второй попытки ввода кода</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Ввести в поле «Код из СМС» код из СМС, отправленного на шаге 3</t>
+          <t>Ввести в поле «Код из СМС» код из СМС, отправленного на шаге 3, и нажать «Подписать»</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Кнопка «Подписать» активна</t>
+          <t>Заявка в статусе «Исполнена», подтверждение контролёром не требуется</t>
         </is>
       </c>
     </row>
@@ -4105,12 +4105,12 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Подписать»</t>
+          <t>Обновить продуктовый профиль клиента</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», подтверждение контролёром не требуется</t>
+          <t>В блоке «Счета» счёт 40817810800000089012 в статусе «Закрыт»</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Обновить продуктовый профиль клиента</t>
+          <t>Напротив счёта 40817810800000089012 нажать «Показать», затем «Операции»</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>В блоке «Счета» счёт 40817810800000089012 в статусе «Закрыт»</t>
+          <t>В списке операций нет «Закрыть счёт»</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Нажать кнопку в окне «Обратите внимание»</t>
+          <t>Нажать «Продолжить»</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Создание клиента: возраст 14 лет</t>
+          <t>Создание клиента: граница возраста 14 лет — младше отказ, в день 14-летия создание</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Открыть карточку»</t>
+          <t>Закрыть сообщение и повторно нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Открылась карточка клиента Лосева Инна Павловна, паспорт 4510 555777</t>
+          <t>Снова выводится сообщение «Клиент с таким паспортом уже существует», карточка не создаётся</t>
         </is>
       </c>
     </row>
@@ -5239,12 +5239,12 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Вернуться в анкету и нажать «Отмена»</t>
+          <t>Нажать «Открыть карточку»</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Анкета закрыта без сохранения, открыта страница «Поиск клиента»</t>
+          <t>Открылась карточка клиента Лосева Инна Павловна, паспорт 4510 555777</t>
         </is>
       </c>
     </row>
@@ -5564,31 +5564,51 @@
       </c>
     </row>
     <row r="234">
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 10</t>
-        </is>
-      </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
-        </is>
-      </c>
-      <c r="I234" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K234" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>900901</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; Общие шаги</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Вход в ЕФР в роли менеджера-операциониста</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>3/11/2025 09:40:12</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Шаг 11</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -5606,469 +5626,383 @@
           <t>tst_oper01</t>
         </is>
       </c>
-      <c r="K235" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
-        </is>
-      </c>
     </row>
     <row r="236">
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 12</t>
-        </is>
-      </c>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить поиск по паспорту 4524 600602</t>
-        </is>
-      </c>
-      <c r="I236" s="2" t="inlineStr">
-        <is>
-          <t>Клиент не найден</t>
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>900902</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; Общие шаги</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Вход в ЕФР в роли финансового консультанта</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>3/11/2025 09:44:37</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>900901</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>tst_fk01</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>900903</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>Вход в ЕФР в роли менеджера-операциониста</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Вход в ЕФР в роли клиентского менеджера</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M237" s="2" t="inlineStr">
+      <c r="M238" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N237" s="2" t="inlineStr">
+      <c r="N238" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O237" s="2" t="inlineStr">
-        <is>
-          <t>3/11/2025 09:40:12</t>
-        </is>
-      </c>
-      <c r="P237" s="2" t="inlineStr">
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>3/11/2025 09:47:05</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="E238" s="2" t="inlineStr">
+    <row r="239">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I238" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>900902</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>tst_kmtp01</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>900904</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>Вход в ЕФР в роли финансового консультанта</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Вход в роли контролёра</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M239" s="2" t="inlineStr">
+      <c r="M240" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N239" s="2" t="inlineStr">
+      <c r="N240" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O239" s="2" t="inlineStr">
-        <is>
-          <t>3/11/2025 09:44:37</t>
-        </is>
-      </c>
-      <c r="P239" s="2" t="inlineStr">
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>3/11/2025 09:52:19</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="E240" s="2" t="inlineStr">
+    <row r="241">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
-        </is>
-      </c>
-      <c r="I240" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J240" s="2" t="inlineStr">
-        <is>
-          <t>tst_fk01</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>900903</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>900905</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>Вход в ЕФР в роли клиентского менеджера</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Поиск клиента по паспорту</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M241" s="2" t="inlineStr">
+      <c r="M242" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N241" s="2" t="inlineStr">
+      <c r="N242" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O241" s="2" t="inlineStr">
-        <is>
-          <t>3/11/2025 09:47:05</t>
-        </is>
-      </c>
-      <c r="P241" s="2" t="inlineStr">
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>3/12/2025 14:05:51</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>Людмила Жаркова</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>900906</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; Общие шаги</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Выход из ЕФР</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>3/12/2025 14:11:26</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>Людмила Жаркова</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница входа в ЕФР</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>900907</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; Общие шаги</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Открытие заявки контролёром</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>8/04/2025 12:41:12</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="E242" s="2" t="inlineStr">
+    <row r="247">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
-        </is>
-      </c>
-      <c r="I242" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J242" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>900904</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; Общие шаги</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>Вход в роли контролёра</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M243" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="N243" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O243" s="2" t="inlineStr">
-        <is>
-          <t>3/11/2025 09:52:19</t>
-        </is>
-      </c>
-      <c r="P243" s="2" t="inlineStr">
-        <is>
-          <t>Максим Гаврилин</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
-        </is>
-      </c>
-      <c r="I244" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J244" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>900905</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; Общие шаги</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>Поиск клиента по паспорту</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M245" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="N245" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O245" s="2" t="inlineStr">
-        <is>
-          <t>3/12/2025 14:05:51</t>
-        </is>
-      </c>
-      <c r="P245" s="2" t="inlineStr">
-        <is>
-          <t>Людмила Жаркова</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
-        </is>
-      </c>
-      <c r="I246" s="2" t="inlineStr">
-        <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>900906</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; Общие шаги</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>Выход из ЕФР</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M247" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="N247" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O247" s="2" t="inlineStr">
-        <is>
-          <t>3/12/2025 14:11:26</t>
-        </is>
-      </c>
-      <c r="P247" s="2" t="inlineStr">
-        <is>
-          <t>Людмила Жаркова</t>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>900907</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; Общие шаги</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>Открытие заявки контролёром</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M249" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="N249" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O249" s="2" t="inlineStr">
-        <is>
-          <t>8/04/2025 12:41:12</t>
-        </is>
-      </c>
-      <c r="P249" s="2" t="inlineStr">
-        <is>
-          <t>Максим Гаврилин</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="E250" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 2</t>
-        </is>
-      </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>

--- a/review-tasks/1b-testcase-review/jury/fixed/testcases.xlsx
+++ b/review-tasks/1b-testcase-review/jury/fixed/testcases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Тест-кейсы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тест-кейсы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q248"/>
+  <dimension ref="A1:Q246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>999,99</t>
+          <t>500,00</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена»</t>
+          <t>Заявка в статусе «Исполнена». В продуктовом профиле клиента в блоке «Вклады» отображается вклад «Надёжный» на 1 000 000,01 ₽ в статусе «Открыт»</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена»</t>
+          <t>Заявка в статусе «Исполнена». В продуктовом профиле клиента в блоке «Вклады» отображается вклад «Пополняемый» на 50 000,00 ₽ в статусе «Открыт»</t>
         </is>
       </c>
     </row>
@@ -2141,2851 +2141,2851 @@
     <row r="74">
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Предусловие 3</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Найти клиента по паспорту из предусловия 2 и подготовить заявку на открытие вклада «Надёжный»: способ внесения «Со счёта или карты в Банке», выбрать текущий счёт клиента, на шаге подписания выбрать текущего пользователя в поле «Уполномоченное лицо банка», нажать «Печать», затем «Документы подписаны»</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Заявка в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Сумма 2 500 000,00; срок 181 день</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Открыть вклад», выбрать вид вклада «Надёжный» и нажать «Далее»</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Открылся шаг «Параметры вклада»</t>
+          <t>Открылась страница входа в ЕФР</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Заполнить параметры вклада, в поле «Счёт списания» выбрать счёт клиента и нажать «Далее»</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Поле «Ставка» = 16,0%. После «Далее» открылся шаг «Печать и подписание»</t>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Сумма 2 500 000,00; срок 181 день; способ внесения «Со счёта или карты в Банке»</t>
+          <t>tst_contr01</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Печать», затем «Документы подписаны»</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница входа в ЕФР</t>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>В поле «Комментарий» ввести причину отклонения и нажать «Отклонить»</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+          <t>Заявка в статусе «Отклонена»</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>tst_contr01</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Комментарий: «Клиент отказался от вклада»</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
+          <t>Войти в ЕФР в роли менеджера-операциониста ТП и найти клиента из предусловия 2</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Открыт продуктовый профиль клиента</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>В поле «Комментарий» ввести причину отклонения и нажать «Отклонить»</t>
+          <t>Проверить блок «Вклады»</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Отклонена»</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>Комментарий: «Клиент отказался от вклада»</t>
+          <t>Вклад «Надёжный» на 2 500 000,00 ₽ в блоке «Вклады» не отображается</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 10</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>900408</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие счёта</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Закрытие текущего счёта: при остатке больше нуля отказ, при нулевом остатке счёт закрывается без контролёра</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Самый высокий</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>9/21/2026 10:31:14</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Павел Ермаков</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>biq90102, account</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Шаг 11</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Войти в ЕФР в роли менеджера-операциониста ТП и найти клиента из предусловия 2</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Открыт продуктовый профиль клиента</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
           <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Шаг 12</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Проверить блок «Вклады»</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>Вклад «Надёжный» на 2 500 000,00 ₽ в блоке «Вклады» не отображается</t>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>У клиента два текущих счёта в рублях в статусе «Открыт»: счёт А с остатком больше нуля, счёт Б с остатком 0,00 ₽</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4517 880901; счёт А 40817810600000023451, остаток 1 500,00 ₽; счёт Б 40817810900000023452, остаток 0,00 ₽</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>900408</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие счёта</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Закрытие текущего счёта: при остатке больше нуля отказ, при нулевом остатке счёт закрывается без контролёра</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>Самый высокий</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>9/21/2026 10:31:14</t>
-        </is>
-      </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>Павел Ермаков</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>biq90102, account</t>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 3</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>У клиента не подключено ДБО</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>У клиента два текущих счёта в рублях в статусе «Открыт»: счёт А с остатком больше нуля, счёт Б с остатком 0,00 ₽</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4517 880901; счёт А 40817810600000023451, остаток 0,01 ₽; счёт Б 40817810900000023452, остаток 0,00 ₽</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>В блоке «Счета» напротив счёта А нажать «Показать», затем «Операции»</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Открыта детальная информация о счёте, в списке операций есть «Закрыть счёт»</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>У клиента не подключено ДБО</t>
+          <t>Шаг 3</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Выбрать «Закрыть счёт»</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Выводится сообщение «Для закрытия счёта остаток должен быть равен 0,00 ₽. Текущий остаток: 1 500,00 ₽», операция не начинается</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Закрыть сообщение. Напротив счёта Б нажать «Показать», затем «Операции» и выбрать «Закрыть счёт»</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Выводится сообщение «У клиента нет полного доступа в ДБО. Электронное подписание недоступно.» с кнопками «Продолжить с бумажным подписанием» и «Отмена»</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>В блоке «Счета» напротив счёта А нажать «Показать», затем «Операции»</t>
+          <t>Нажать «Продолжить с бумажным подписанием»</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Открыта детальная информация о счёте, в списке операций есть «Закрыть счёт»</t>
+          <t>Открылась форма «Закрытие счёта»: счёт 40817810900000023452, остаток 0,00 ₽, способ подписания «Бумажное»</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Выбрать «Закрыть счёт»</t>
+          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя и нажать «Печать»</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Для закрытия счёта остаток должен быть равен 0,00 ₽. Текущий остаток: 0,01 ₽», операция не начинается</t>
+          <t>В новой вкладке открылась печатная форма заявления на закрытие счёта, кнопка «Документы подписаны» стала активна</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Закрыть сообщение. Напротив счёта Б нажать «Показать», затем «Операции» и выбрать «Закрыть счёт»</t>
+          <t>Нажать «Документы подписаны»</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «У клиента нет полного доступа в ДБО. Электронное подписание недоступно.» с кнопками «Продолжить с бумажным подписанием» и «Отмена»</t>
+          <t>Заявка в статусе «Исполнена», сообщение о подтверждении контролёром не выводится</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Продолжить с бумажным подписанием»</t>
+          <t>В продуктовом профиле клиента проверить статус счёта Б в блоке «Счета»</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Открылась форма «Закрытие счёта»: счёт 40817810900000023452, остаток 0,00 ₽, способ подписания «Бумажное»</t>
+          <t>Счёт 40817810900000023452 в статусе «Закрыт»</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 6</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя и нажать «Печать»</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>В новой вкладке открылась печатная форма заявления на закрытие счёта, кнопка «Документы подписаны» стала активна</t>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>900409</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Закрытие вклада без текущего счёта в рублях: операция не продолжается</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>9/21/2026 15:08:52</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Ксения Литвинова</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>biq90102, deposit, negative</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Документы подписаны»</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», сообщение о подтверждении контролёром не выводится. Счёт Б в блоке «Счета» в статусе «Закрыт»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>tst_fk01</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900902 «Вход в ЕФР в роли финансового консультанта»</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>900409</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Закрытие вклада без текущего счёта в рублях: операция не продолжается</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>9/21/2026 15:08:52</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="inlineStr">
-        <is>
-          <t>Ксения Литвинова</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="inlineStr">
-        <is>
-          <t>biq90102, deposit, negative</t>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Клиент с открытым вкладом «Пополняемый». Текущих счетов в рублях у клиента нет, есть текущий счёт в долларах США</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4523 445667; вклад 42305810700000078901; счёт в USD 40817840200000078902</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
+          <t>Предусловие 3</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>tst_fk01</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900902 «Вход в ЕФР в роли финансового консультанта»</t>
+          <t>У клиента подключено ДБО, уровень доступа «Полный»</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Клиент с открытым вкладом «Пополняемый». Текущих счетов в рублях у клиента нет, есть текущий счёт в долларах США</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4523 445667; вклад 42305810700000078901; счёт в USD 40817840200000078902</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>У клиента подключено ДБО, уровень доступа «Полный»</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Напротив вклада 42305810700000078901 нажать «Показать»</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Открыта детальная информация о вкладе, доступна кнопка «Операции»</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Нажать «Операции» и выбрать «Закрыть вклад»</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Выводится сообщение «У клиента нет открытого текущего счёта в рублях. Откройте счёт, чтобы перечислить средства вклада.» с кнопками «Открыть счёт» и «Отмена»</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада 42305810700000078901 нажать «Показать»</t>
+          <t>Нажать «Отмена»</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Открыта детальная информация о вкладе, доступна кнопка «Операции»</t>
+          <t>Сообщение закрыто, открыта детальная информация о вкладе, вклад в статусе «Открыт»</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Операции» и выбрать «Закрыть вклад»</t>
+          <t>Повторно нажать «Операции» и выбрать «Закрыть вклад»</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «У клиента нет открытого текущего счёта в рублях. Откройте счёт, чтобы перечислить средства вклада.» с кнопками «Открыть счёт» и «Отмена»</t>
+          <t>Снова выводится сообщение об отсутствии счёта для перечисления с кнопками «Открыть счёт» и «Отмена»</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отмена»</t>
+          <t>Нажать «Отмена» и обновить продуктовый профиль клиента</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Сообщение закрыто, открыта детальная информация о вкладе, вклад в статусе «Открыт»</t>
+          <t>В блоке «Вклады» вклад 42305810700000078901 в статусе «Открыт»</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 5</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Повторно нажать «Операции» и выбрать «Закрыть вклад»</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>Снова выводится сообщение об отсутствии счёта для перечисления с кнопками «Открыть счёт» и «Отмена»</t>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>900410</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Досрочное закрытие вклада с электронным подписанием</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Самый высокий</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026 09:55:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Ирина Соловьёва</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>biq90102, deposit, dbo</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Отмена» и обновить продуктовый профиль клиента</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>В блоке «Вклады» вклад 42305810700000078901 в статусе «Открыт»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>900410</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Досрочное закрытие вклада с электронным подписанием</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>Самый высокий</t>
-        </is>
-      </c>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>9/22/2026 09:55:20</t>
-        </is>
-      </c>
-      <c r="P107" s="2" t="inlineStr">
-        <is>
-          <t>Ирина Соловьёва</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>biq90102, deposit, dbo</t>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Клиент от 18 лет с вкладом «Надёжный» в статусе «Открыт» и открытым текущим счётом в рублях. Вклад открыт 30 дней назад на срок 181 день</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562, остаток 5 000,00 ₽</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
+          <t>Предусловие 3</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>У клиента подключено ДБО, уровень доступа «Полный»</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>Клиент от 18 лет с вкладом «Надёжный» в статусе «Открыт» и открытым текущим счётом в рублях. Вклад открыт 30 дней назад на срок 181 день</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562, остаток 5 000,00 ₽</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>У клиента подключено ДБО, уровень доступа «Полный»</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Параметры закрытия»</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Проверить сообщения и поля на странице</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Выводится сообщение «Вклад закрывается досрочно. Проценты будут пересчитаны по ставке 0,01% годовых.» В поле «Сумма к выплате» — 100 000,82 ₽</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>Открыть список «Счёт для перечисления»</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия»</t>
+          <t>В списке только текущие рублёвые счета клиента: 40817810300000034562</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Проверить сообщения и поля на странице</t>
+          <t>Выбрать счёт из предусловия и нажать «Далее»</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Вклад закрывается досрочно. Проценты будут пересчитаны по ставке 0,01% годовых.» В поле «Сумма к выплате» — 100 000,82 ₽</t>
+          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Открыть список «Счёт для перечисления»</t>
+          <t>Нажать «Отправить код»</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>В списке только текущие рублёвые счета клиента: 40817810300000034562</t>
+          <t>Клиенту отправлено СМС с кодом, доступно поле «Код из СМС»</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Выбрать счёт из предусловия и нажать «Далее»</t>
+          <t>Ввести код в поле «Код из СМС» и нажать «Подписать»</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
+          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», подтверждение контролёром не требуется</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Код из СМС, пришедшего на тестовый номер клиента</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отправить код»</t>
+          <t>Напротив счёта 40817810300000034562 нажать «Показать»</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Клиенту отправлено СМС с кодом, доступно поле «Код из СМС»</t>
+          <t>Остаток счёта — 105 000,82 ₽</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 7</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Ввести код в поле «Код из СМС» и нажать «Подписать»</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», подтверждение контролёром не требуется</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>Код из СМС, пришедшего на тестовый номер клиента</t>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>900411</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Несовершеннолетний клиент</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Закрытие вклада несовершеннолетнему клиенту с участием законного представителя</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>9/22/2026 14:17:36</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>Ксения Литвинова</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>biq90102, deposit, minor</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Напротив счёта 40817810300000034562 нажать «Показать»</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Остаток счёта — 105 000,82 ₽</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>900411</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Несовершеннолетний клиент</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Закрытие вклада несовершеннолетнему клиенту с участием законного представителя</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M119" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="N119" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>9/22/2026 14:17:36</t>
-        </is>
-      </c>
-      <c r="P119" s="2" t="inlineStr">
-        <is>
-          <t>Ксения Литвинова</t>
-        </is>
-      </c>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>biq90102, deposit, minor</t>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Клиенту 16 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4519 001223; вклад 42301810500000045671; счёт 40817810700000045672</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
+          <t>Предусловие 3</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+          <t>Законный представитель клиента — клиент Банка</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Паспорт представителя 4501 334455</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>Клиенту 16 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4519 001223; вклад 42301810500000045671; счёт 40817810700000045672</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Законный представитель клиента — клиент Банка</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт представителя 4501 334455</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Клиенту меньше 18 лет. Операция проводится с участием законного представителя.», отображается блок «Законный представитель», кнопка «Далее» неактивна. Запомнить значение поля «Сумма к выплате»</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>В блоке «Законный представитель» найти представителя по паспорту и выбрать его</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>В блоке отображаются ФИО и паспорт представителя</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Клиенту меньше 18 лет. Операция проводится с участием законного представителя.», отображается блок «Законный представитель», кнопка «Далее» неактивна. Запомнить значение поля «Сумма к выплате»</t>
+          <t>В поле «Счёт для перечисления» — 40817810700000045672</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>В блоке «Законный представитель» найти представителя по паспорту и выбрать его</t>
+          <t>Нажать «Далее»</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>В блоке отображаются ФИО и паспорт представителя</t>
+          <t>Открылась страница «Подписание», доступен только способ подписания «Бумажное». Сообщение об отсутствии полного доступа в ДБО не выводится</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
+          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Печать», затем «Документы подписаны»</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» — 40817810700000045672</t>
+          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Далее»</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», доступен только способ подписания «Бумажное». Сообщение об отсутствии полного доступа в ДБО не выводится</t>
+          <t>Открылась страница входа в ЕФР</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Печать», затем «Документы подписаны»</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 9</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 10</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 11</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
-        </is>
-      </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Нажать «Подтвердить»</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», сумма из поля «Сумма к выплате» (шаг 2) зачислена на счёт 40817810700000045672</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 10</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>900412</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Несовершеннолетний клиент</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Закрытие вклада в день 18-летия клиента: без законного представителя, электронное подписание со второй попытки ввода кода</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>9/23/2026 10:44:03</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>Ирина Соловьёва</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>biq90102, deposit, dbo</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Шаг 11</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Подтвердить»</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», сумма из поля «Сумма к выплате» (шаг 2) зачислена на счёт 40817810700000045672</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>900412</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Несовершеннолетний клиент</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Закрытие вклада в день 18-летия клиента: без законного представителя, электронное подписание со второй попытки ввода кода</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M134" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="N134" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O134" s="2" t="inlineStr">
-        <is>
-          <t>9/23/2026 10:44:03</t>
-        </is>
-      </c>
-      <c r="P134" s="2" t="inlineStr">
-        <is>
-          <t>Ирина Соловьёва</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>biq90102, deposit, dbo</t>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Клиенту сегодня исполняется 18 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4520 112334; дата рождения — сегодняшняя дата 18 лет назад; вклад 42301810800000056781; счёт 40817810100000056782</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Клиенту сегодня исполняется 18 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4520 112334; дата рождения — сегодняшняя дата 18 лет назад; вклад 42301810800000056781; счёт 40817810100000056782</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Параметры закрытия», блок «Законный представитель» не отображается</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Проверить сообщения на странице</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Сообщение о досрочном закрытии не выводится. Запомнить значение поля «Сумма к выплате»</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия и нажать «Далее»</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия», блок «Законный представитель» не отображается</t>
+          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Проверить сообщения на странице</t>
+          <t>Нажать «Отправить код»</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Сообщение о досрочном закрытии не выводится. Запомнить значение поля «Сумма к выплате»</t>
+          <t>Клиенту отправлено СМС с кодом, доступно поле «Код из СМС»</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия и нажать «Далее»</t>
+          <t>Ввести в поле «Код из СМС» неверный код и нажать «Подписать»</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
+          <t>Выводится сообщение «Неверный код. Осталось попыток: 2»</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>000000</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отправить код»</t>
+          <t>Ввести верный код из СМС и нажать «Подписать»</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Клиенту отправлено СМС с кодом, доступно поле «Код из СМС»</t>
+          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», подтверждение контролёром не требуется</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Ввести в поле «Код из СМС» неверный код и нажать «Подписать»</t>
+          <t>Открыть счёт для перечисления</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Неверный код. Осталось попыток: 2»</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>000000</t>
+          <t>В истории операций счёта есть зачисление с вклада 42301810800000056781 на сумму из поля «Сумма к выплате» (шаг 3)</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 7</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>Ввести верный код из СМС и нажать «Подписать»</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», подтверждение контролёром не требуется</t>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>900413</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Закрытие вклада без полного доступа в ДБО: бумажное подписание и подтверждение контролёром</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>Самый высокий</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>9/23/2026 16:02:48</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>Павел Ермаков</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>biq90102, deposit, control</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>Открыть счёт для перечисления</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>В истории операций счёта есть зачисление с вклада 42301810800000056781 на сумму из поля «Сумма к выплате» (шаг 3)</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>900413</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Закрытие вклада без полного доступа в ДБО: бумажное подписание и подтверждение контролёром</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M145" s="2" t="inlineStr">
-        <is>
-          <t>Самый высокий</t>
-        </is>
-      </c>
-      <c r="N145" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O145" s="2" t="inlineStr">
-        <is>
-          <t>9/23/2026 16:02:48</t>
-        </is>
-      </c>
-      <c r="P145" s="2" t="inlineStr">
-        <is>
-          <t>Павел Ермаков</t>
-        </is>
-      </c>
-      <c r="Q145" s="2" t="inlineStr">
-        <is>
-          <t>biq90102, deposit, control</t>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Клиент от 18 лет с вкладом «Пополняемый» в статусе «Открыт», срок вклада не закончился, и текущим счётом в рублях. ДБО подключено, уровень доступа «Ограниченный»</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4521 223445; вклад 42305810400000067891, сумма 50 000,00 ₽, открыт 73 дня назад на срок 181 день; счёт 40817810400000067892</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>Клиент от 18 лет с вкладом «Пополняемый» в статусе «Открыт», срок вклада не закончился, и текущим счётом в рублях. ДБО подключено, уровень доступа «Ограниченный»</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4521 223445; вклад 42305810400000067891, сумма 50 000,00 ₽, открыт 73 дня назад на срок 181 день; счёт 40817810400000067892</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Выводится сообщение «У клиента нет полного доступа в ДБО. Электронное подписание недоступно.» с кнопками «Продолжить с бумажным подписанием» и «Отмена»</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Нажать «Продолжить с бумажным подписанием»</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Вклад закрывается досрочно. Проценты будут пересчитаны по ставке 0,01% годовых.» В поле «Сумма к выплате» — 50 001,00 ₽</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «У клиента нет полного доступа в ДБО. Электронное подписание недоступно.» с кнопками «Продолжить с бумажным подписанием» и «Отмена»</t>
+          <t>В поле «Счёт для перечисления» — 40817810400000067892</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Продолжить с бумажным подписанием»</t>
+          <t>Нажать «Далее»</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Вклад закрывается досрочно. Проценты будут пересчитаны по ставке 0,01% годовых.» В поле «Сумма к выплате» — 50 001,00 ₽</t>
+          <t>Открылась страница «Подписание», способ подписания «Бумажное»</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
+          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Печать», затем «Документы подписаны»</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» — 40817810400000067892</t>
+          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Далее»</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», способ подписания «Бумажное»</t>
+          <t>Открылась страница входа в ЕФР</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Печать», затем «Документы подписаны»</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 9</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 10</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 11</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Нажать «Подтвердить»</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», на счёт 40817810400000067892 зачислено 50 001,00 ₽</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 10</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>900414</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие счёта</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Закрытие текущего счёта с нулевым остатком, электронное подписание</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>9/24/2026 11:20:15</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>Павел Ермаков</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>biq90102, account, dbo</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Шаг 11</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Подтвердить»</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», на счёт 40817810400000067892 зачислено 50 001,00 ₽</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>900414</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие счёта</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Закрытие текущего счёта с нулевым остатком, электронное подписание</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M159" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="N159" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O159" s="2" t="inlineStr">
-        <is>
-          <t>9/24/2026 11:20:15</t>
-        </is>
-      </c>
-      <c r="P159" s="2" t="inlineStr">
-        <is>
-          <t>Павел Ермаков</t>
-        </is>
-      </c>
-      <c r="Q159" s="2" t="inlineStr">
-        <is>
-          <t>biq90102, account, dbo</t>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>У клиента текущий (не карточный) счёт в рублях с остатком 0,00 ₽, ДБО подключено с полным доступом</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4522 334556; счёт 40817810800000089012</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>У клиента текущий (не карточный) счёт в рублях с остатком 0,00 ₽, ДБО подключено с полным доступом</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4522 334556; счёт 40817810800000089012</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Напротив счёта нажать «Показать», затем «Операции» и выбрать «Закрыть счёт»</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Открылась форма «Закрытие счёта», остаток 0,00 ₽, выбран способ подписания «Электронное»</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Нажать «Отправить код»</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Клиенту отправлено СМС, доступно поле «Код из СМС»</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Напротив счёта нажать «Показать», затем «Операции» и выбрать «Закрыть счёт»</t>
+          <t>Ввести в поле «Код из СМС» код из СМС, отправленного на шаге 3, и нажать «Подписать»</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Открылась форма «Закрытие счёта», остаток 0,00 ₽, выбран способ подписания «Электронное»</t>
+          <t>Заявка в статусе «Исполнена», подтверждение контролёром не требуется</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отправить код»</t>
+          <t>Обновить продуктовый профиль клиента</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Клиенту отправлено СМС, доступно поле «Код из СМС»</t>
+          <t>В блоке «Счета» счёт 40817810800000089012 в статусе «Закрыт»</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Ввести в поле «Код из СМС» код из СМС, отправленного на шаге 3, и нажать «Подписать»</t>
+          <t>Напротив счёта 40817810800000089012 нажать «Показать», затем «Операции»</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», подтверждение контролёром не требуется</t>
+          <t>В списке операций нет «Закрыть счёт»</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 5</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Обновить продуктовый профиль клиента</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>В блоке «Счета» счёт 40817810800000089012 в статусе «Закрыт»</t>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>900415</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Создание клиента: совпали ФИО и дата рождения, нет предыдущего паспорта — подтверждение контролёром</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Самый высокий</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>9/28/2026 10:09:27</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>Дарья Мельникова</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>biq90103, client, duplicate, control</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Напротив счёта 40817810800000089012 нажать «Показать», затем «Операции»</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>В списке операций нет «Закрыть счёт»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>tst_kmtp01</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>900415</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Создание клиента: совпали ФИО и дата рождения, нет предыдущего паспорта — подтверждение контролёром</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M168" s="2" t="inlineStr">
-        <is>
-          <t>Самый высокий</t>
-        </is>
-      </c>
-      <c r="N168" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O168" s="2" t="inlineStr">
-        <is>
-          <t>9/28/2026 10:09:27</t>
-        </is>
-      </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>Дарья Мельникова</t>
-        </is>
-      </c>
-      <c r="Q168" s="2" t="inlineStr">
-        <is>
-          <t>biq90103, client, duplicate, control</t>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>В ЕФР есть клиент Семёнова Алёна Игоревна с датой рождения 12.03.1990</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт существующего клиента 4512 300111</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>В ЕФР есть клиент Семёнова Алёна Игоревна с датой рождения 12.03.1990</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Ввести ФИО и дату рождения нового клиента</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>В полях отображаются введённые значения</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Паспорт существующего клиента 4512 300111</t>
+          <t>Фамилия СЕМЕНОВА, имя АЛЕНА, отчество ИГОРЕВНА, дата рождения 12.03.1990</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
+          <t>Заполнить остальные обязательные поля анкеты значениями из тестовых данных</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Все обязательные поля анкеты заполнены</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Пол женский; паспорт 4520 300222, выдан 18.03.2026, код подразделения 500-105, ГУ МВД России по Московской обл.; телефон +7 900 555-66-77; адрес: г. Москва, ул. Тестовая, д. 3, кв. 21</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Ввести ФИО и дату рождения нового клиента</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>В полях отображаются введённые значения</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>Фамилия СЕМЕНОВА, имя АЛЕНА, отчество ИГОРЕВНА, дата рождения 12.03.1990</t>
+          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Заполнить остальные обязательные поля анкеты значениями из тестовых данных</t>
+          <t>Нажать «Нет предыдущего паспорта»</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Все обязательные поля анкеты заполнены</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>Пол женский; паспорт 4520 300222, выдан 18.03.2026, код подразделения 500-105, ГУ МВД России по Московской обл.; телефон +7 900 555-66-77; адрес: г. Москва, ул. Тестовая, д. 3, кв. 21</t>
+          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
+          <t>Открылась страница входа в ЕФР</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Нет предыдущего паспорта»</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 9</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 10</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
-        </is>
-      </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Проверить блок «Внимание» на форме заявки</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Выводится уведомление «Возможен дубль клиента. Проверьте данные в АБС перед подтверждением.» и данные найденного клиента: Семёнова Алёна Игоревна, 12.03.1990, паспорт 4512 300111</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 11</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
+          <t>Нажать «Подтвердить операцию»</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
-        </is>
-      </c>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен»</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 10</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>Проверить блок «Внимание» на форме заявки</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>Выводится уведомление «Возможен дубль клиента. Проверьте данные в АБС перед подтверждением.» и данные найденного клиента: Семёнова Алёна Игоревна, 12.03.1990, паспорт 4512 300111</t>
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>900416</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Создание клиента: предыдущий паспорт принадлежит найденному клиенту — новая карточка не создаётся</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>9/28/2026 14:51:06</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>Дарья Мельникова</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>biq90103, client, duplicate</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Шаг 11</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Подтвердить операцию»</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>900416</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Создание клиента: предыдущий паспорт принадлежит найденному клиенту — новая карточка не создаётся</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M182" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O182" s="2" t="inlineStr">
-        <is>
-          <t>9/28/2026 14:51:06</t>
-        </is>
-      </c>
-      <c r="P182" s="2" t="inlineStr">
-        <is>
-          <t>Дарья Мельникова</t>
-        </is>
-      </c>
-      <c r="Q182" s="2" t="inlineStr">
-        <is>
-          <t>biq90103, client, duplicate</t>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>В ЕФР есть клиент Карпов Олег Дмитриевич, дата рождения 05.07.1985, текущий паспорт 4515 404001, прежний паспорт 4505 404000</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K183" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>В ЕФР есть клиент Карпов Олег Дмитриевич, дата рождения 05.07.1985, текущий паспорт 4515 404001, прежний паспорт 4505 404000</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Заполнить анкету: ФИО и дата рождения — как у клиента из предусловия 2, новый паспорт, остальные поля — из тестовых данных</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>В анкете заполнены все обязательные поля</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Карпов Олег Дмитриевич, 05.07.1985, пол мужской; паспорт 4521 404002, выдан 10.08.2025, код подразделения 500-112, ГУ МВД России по Московской обл.; телефон +7 900 111-22-33; адрес: г. Москва, ул. Тестовая, д. 1, кв. 1</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Заполнить анкету: ФИО и дата рождения — как у клиента из предусловия 2, новый паспорт, остальные поля — из тестовых данных</t>
+          <t>Нажать «Ввести данные предыдущего паспорта»</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>В анкете заполнены все обязательные поля</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>Карпов Олег Дмитриевич, 05.07.1985, пол мужской; паспорт 4521 404002, выдан 10.08.2025, код подразделения 500-112, ГУ МВД России по Московской обл.; телефон +7 900 111-22-33; адрес: г. Москва, ул. Тестовая, д. 1, кв. 1</t>
+          <t>Открылись поля «Серия», «Номер» и кнопка «Проверить»</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>Ввести серию и номер предыдущего паспорта клиента</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
+          <t>В полях «Серия» и «Номер» — 4505 и 404000</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>4505 404000</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Ввести данные предыдущего паспорта»</t>
+          <t>Нажать «Проверить»</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Открылись поля «Серия», «Номер» и кнопка «Проверить»</t>
+          <t>Выводится сообщение «Найден клиент с этим паспортом. Обновите паспорт в карточке существующего клиента.» и кнопка «Открыть карточку»</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Ввести серию и номер предыдущего паспорта клиента</t>
+          <t>Нажать «Открыть карточку»</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>В полях «Серия» и «Номер» — 4505 и 404000</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="inlineStr">
-        <is>
-          <t>4505 404000</t>
+          <t>Открылась карточка клиента Карпов Олег Дмитриевич, 05.07.1985, паспорт 4515 404001</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Проверить»</t>
+          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4521 404002</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Найден клиент с этим паспортом. Обновите паспорт в карточке существующего клиента.» и кнопка «Открыть карточку»</t>
+          <t>Клиент не найден</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 7</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Открыть карточку»</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr">
-        <is>
-          <t>Открылась карточка клиента Карпов Олег Дмитриевич, 05.07.1985, паспорт 4515 404001</t>
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>900417</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Списки финмониторинга</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Создание клиента: совпадение со списком финмониторинга, операция продолжается</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>Самый высокий</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>9/29/2026 11:34:40</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>Владимир Астахов</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>biq90103, client, finmon</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4521 404002</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Клиент не найден</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>tst_kmtp01</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>900417</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Списки финмониторинга</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>Создание клиента: совпадение со списком финмониторинга, операция продолжается</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M193" s="2" t="inlineStr">
-        <is>
-          <t>Самый высокий</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O193" s="2" t="inlineStr">
-        <is>
-          <t>9/29/2026 11:34:40</t>
-        </is>
-      </c>
-      <c r="P193" s="2" t="inlineStr">
-        <is>
-          <t>Владимир Астахов</t>
-        </is>
-      </c>
-      <c r="Q193" s="2" t="inlineStr">
-        <is>
-          <t>biq90103, client, finmon</t>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Подготовлены данные человека из списка «Решения межведомственной комиссии». В ЕФР его нет</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>Гусев Роман Ильич, 14.02.1979, пол мужской; паспорт 4518 700701, выдан 03.03.2024, код подразделения 770-045, ГУ МВД России по г. Москве; телефон +7 900 222-33-44; адрес: г. Москва, ул. Тестовая, д. 5, кв. 12</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
-        </is>
-      </c>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>Подготовлены данные человека из списка «Решения межведомственной комиссии». В ЕФР его нет</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>Гусев Роман Ильич, 14.02.1979, пол мужской; паспорт 4518 700701, выдан 03.03.2024, код подразделения 770-045, ГУ МВД России по г. Москве; телефон +7 900 222-33-44; адрес: г. Москва, ул. Тестовая, д. 5, кв. 12</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Заполнить анкету данными из предусловия 2 и нажать «Сохранить»</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Открылось окно «Обратите внимание» с текстом «Выявлено совпадение данных клиента со списком: Решения межведомственной комиссии. Вы можете продолжить операцию. Информация будет передана в финмониторинг.»</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
+          <t>Проверить кнопки в окне</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>В окне доступна кнопка «Продолжить»</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Заполнить анкету данными из предусловия 2 и нажать «Сохранить»</t>
+          <t>Нажать «Продолжить»</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Выявлено совпадение данных клиента со списком: Решения межведомственной комиссии. Вы можете продолжить операцию. Информация будет передана в финмониторинг.»</t>
+          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен», подтверждение контролёром не требуется</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Проверить кнопки в окне</t>
+          <t>Открыть карточку клиента, вкладку «История операций»</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>В окне доступна кнопка «Продолжить»</t>
+          <t>В истории есть запись «Передано в финмониторинг»</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Продолжить»</t>
+          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4518 700701</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен», подтверждение контролёром не требуется</t>
+          <t>Клиент найден, статус «Активен»</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 5</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>Открыть карточку клиента, вкладку «История операций»</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="inlineStr">
-        <is>
-          <t>В истории есть запись «Передано в финмониторинг»</t>
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>900418</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Анкета</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Создание клиента: граница возраста 14 лет — младше отказ, в день 14-летия создание</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>9/29/2026 16:12:58</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>Владимир Астахов</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>biq90103, client, age</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4518 700701</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, статус «Активен»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>900418</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Анкета</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>Создание клиента: граница возраста 14 лет — младше отказ, в день 14-летия создание</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M202" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="N202" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O202" s="2" t="inlineStr">
-        <is>
-          <t>9/29/2026 16:12:58</t>
-        </is>
-      </c>
-      <c r="P202" s="2" t="inlineStr">
-        <is>
-          <t>Владимир Астахов</t>
-        </is>
-      </c>
-      <c r="Q202" s="2" t="inlineStr">
-        <is>
-          <t>biq90103, client, age</t>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Заполнить обязательные поля анкеты, кроме даты рождения, значениями из тестовых данных</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+          <t>Поля анкеты заполнены значениями из тестовых данных</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Белова Ника Андреевна, пол женский; паспорт 4525 800801, выдан сегодня, код подразделения 500-120, ГУ МВД России по Московской обл.; телефон +7 900 666-77-88; адрес: г. Москва, ул. Тестовая, д. 21, кв. 2</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
+          <t>В поле «Дата рождения» ввести дату, при которой клиенту меньше 14 лет</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Дата отображается в поле</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>Сегодняшняя дата 14 лет назад плюс один день: клиенту 14 лет исполнится завтра</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Заполнить обязательные поля анкеты, кроме даты рождения, значениями из тестовых данных</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Поля анкеты заполнены значениями из тестовых данных</t>
-        </is>
-      </c>
-      <c r="J205" s="2" t="inlineStr">
-        <is>
-          <t>Белова Ника Андреевна, пол женский; паспорт 4525 800801, выдан сегодня, код подразделения 500-120, ГУ МВД России по Московской обл.; телефон +7 900 666-77-88; адрес: г. Москва, ул. Тестовая, д. 21, кв. 2</t>
+          <t>Выводится сообщение «Клиенту меньше 14 лет. Создание клиента по паспорту РФ невозможно.», карточка не создана</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>В поле «Дата рождения» ввести дату, при которой клиенту меньше 14 лет</t>
+          <t>Изменить дату рождения так, чтобы клиенту сегодня исполнилось 14 лет</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
@@ -4995,14 +4995,14 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>Сегодняшняя дата 14 лет назад плюс один день: клиенту 14 лет исполнится завтра</t>
+          <t>Сегодняшняя дата 14 лет назад</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -5012,561 +5012,586 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Клиенту меньше 14 лет. Создание клиента по паспорту РФ невозможно.», карточка не создана</t>
+          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен»</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Изменить дату рождения так, чтобы клиенту сегодня исполнилось 14 лет</t>
+          <t>Выполнить поиск клиента по паспорту из анкеты</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Дата отображается в поле</t>
-        </is>
-      </c>
-      <c r="J208" s="2" t="inlineStr">
-        <is>
-          <t>Сегодняшняя дата 14 лет назад</t>
+          <t>Клиент найден: Белова Ника Андреевна, дата рождения — из шага 5, статус «Активен»</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 6</t>
-        </is>
-      </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Сохранить»</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен»</t>
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>900419</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Создание клиента: дубль по паспорту</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>Самый высокий</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>9/30/2026 09:47:13</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>Дарья Мельникова</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>biq90103, client, duplicate, negative</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
-        </is>
-      </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить поиск клиента по паспорту из анкеты</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден: Белова Ника Андреевна, дата рождения — из шага 5, статус «Активен»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>tst_kmtp01</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>900419</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>Создание клиента: дубль по паспорту</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M211" s="2" t="inlineStr">
-        <is>
-          <t>Самый высокий</t>
-        </is>
-      </c>
-      <c r="N211" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O211" s="2" t="inlineStr">
-        <is>
-          <t>9/30/2026 09:47:13</t>
-        </is>
-      </c>
-      <c r="P211" s="2" t="inlineStr">
-        <is>
-          <t>Дарья Мельникова</t>
-        </is>
-      </c>
-      <c r="Q211" s="2" t="inlineStr">
-        <is>
-          <t>biq90103, client, duplicate, negative</t>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>В ЕФР есть клиент Лосева Инна Павловна, 30.09.1988, паспорт 4510 555777</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
+          <t>Предусловие 3</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J212" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
-        </is>
-      </c>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>В ЕФР есть клиент Лосева Инна Павловна, 30.09.1988, паспорт 4510 555777</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Убедиться, что поле «Гражданство» содержит «РФ» и недоступно для редактирования. Заполнить анкету: ФИО и дата рождения — другие, паспорт — клиента из предусловия 2</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>В анкете заполнены все обязательные поля</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>Лосев Артём Викторович, 17.01.1991, пол мужской; паспорт 4510 555777, выдан 22.04.2023, код подразделения 500-031, ГУ МВД России по Московской обл.; телефон +7 900 333-44-55; адрес: г. Москва, ул. Тестовая, д. 9, кв. 3</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Выводится сообщение «Клиент с таким паспортом уже существует» и кнопка «Открыть карточку». Окно о совпадении ФИО и проверки по спискам не выводятся</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Заполнить анкету: ФИО и дата рождения — другие, паспорт — клиента из предусловия 2</t>
+          <t>Закрыть сообщение и повторно нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>В анкете заполнены все обязательные поля</t>
-        </is>
-      </c>
-      <c r="J215" s="2" t="inlineStr">
-        <is>
-          <t>Лосев Артём Викторович, 17.01.1991, пол мужской; паспорт 4510 555777, выдан 22.04.2023, код подразделения 500-031, ГУ МВД России по Московской обл.; телефон +7 900 333-44-55; адрес: г. Москва, ул. Тестовая, д. 9, кв. 3</t>
+          <t>Снова выводится сообщение «Клиент с таким паспортом уже существует», карточка не создаётся</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>Нажать «Открыть карточку»</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Клиент с таким паспортом уже существует» и кнопка «Открыть карточку». Окно о совпадении ФИО и проверки по спискам не выводятся</t>
+          <t>Открылась карточка клиента Лосева Инна Павловна, паспорт 4510 555777</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Закрыть сообщение и повторно нажать «Сохранить»</t>
+          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4510 555777</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Снова выводится сообщение «Клиент с таким паспортом уже существует», карточка не создаётся</t>
+          <t>Найден один клиент</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Открыть карточку»</t>
+          <t>Открыть карточку найденного клиента</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Открылась карточка клиента Лосева Инна Павловна, паспорт 4510 555777</t>
+          <t>ФИО, дата рождения и паспорт — клиента из предусловия 2: Лосева Инна Павловна, 30.09.1988, 4510 555777</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 6</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4510 555777</t>
-        </is>
-      </c>
-      <c r="I219" s="2" t="inlineStr">
-        <is>
-          <t>Найден один клиент</t>
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>900420</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Создание клиента: дубль без предыдущего паспорта и совпадение со списком — контролёр отменяет создание</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>10/01/2026 13:25:39</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>Владимир Астахов</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>biq90103, client, duplicate, finmon, control</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>Открыть карточку найденного клиента</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>ФИО, дата рождения и паспорт — клиента из предусловия 2: Лосева Инна Павловна, 30.09.1988, 4510 555777</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>900420</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>Создание клиента: дубль без предыдущего паспорта и совпадение со списком — контролёр отменяет создание</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M221" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="N221" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O221" s="2" t="inlineStr">
-        <is>
-          <t>10/01/2026 13:25:39</t>
-        </is>
-      </c>
-      <c r="P221" s="2" t="inlineStr">
-        <is>
-          <t>Владимир Астахов</t>
-        </is>
-      </c>
-      <c r="Q221" s="2" t="inlineStr">
-        <is>
-          <t>biq90103, client, duplicate, finmon, control</t>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>В ЕФР есть клиент Рябова Дарья Сергеевна, 21.11.1992, паспорт 4514 600601</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 1</t>
+          <t>Предусловие 3</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+          <t>Данные нового человека: Рябова Дарья Сергеевна, 21.11.1992, паспорт другой. Человек входит в список «Решения межведомственной комиссии»</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
+          <t>Пол женский; паспорт 4524 600602, выдан 15.06.2026, код подразделения 500-118, ГУ МВД России по Московской обл.; телефон +7 900 444-55-66; адрес: г. Москва, ул. Тестовая, д. 14, кв. 7</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>В ЕФР есть клиент Рябова Дарья Сергеевна, 21.11.1992, паспорт 4514 600601</t>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Нажать «Создать клиента», заполнить анкету данными из предусловия 3 и нажать «Сохранить»</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>Данные нового человека: Рябова Дарья Сергеевна, 21.11.1992, паспорт другой. Человек входит в список «Решения межведомственной комиссии»</t>
-        </is>
-      </c>
-      <c r="J224" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4524 600602, выдан 15.06.2026, код подразделения 500-118, ГУ МВД России по Московской обл.; телефон +7 900 444-55-66; адрес: г. Москва, ул. Тестовая, д. 14, кв. 7</t>
+          <t>Шаг 2</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Нажать «Нет предыдущего паспорта»</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>Открылось окно «Обратите внимание» с текстом «Выявлено совпадение данных клиента со списком: Решения межведомственной комиссии. Вы можете продолжить операцию. Информация будет передана в финмониторинг.» и кнопкой «Продолжить»</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Создать клиента», заполнить анкету данными из предусловия 3 и нажать «Сохранить»</t>
+          <t>Нажать «Продолжить»</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
+          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Нет предыдущего паспорта»</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Выявлено совпадение данных клиента со списком: Решения межведомственной комиссии. Вы можете продолжить операцию. Информация будет передана в финмониторинг.» и кнопкой «Продолжить»</t>
+          <t>Открылась страница входа в ЕФР</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Продолжить»</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
-        </is>
-      </c>
-      <c r="I228" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J229" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
-        </is>
-      </c>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Проверить блок «Внимание» на форме заявки</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Выводится уведомление «Возможен дубль клиента. Проверьте данные в АБС перед подтверждением.» и данные найденного клиента: Рябова Дарья Сергеевна, 21.11.1992, паспорт 4514 600601</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 9</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
+          <t>В поле «Комментарий» ввести причину и нажать «Отменить операцию»</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
-        </is>
-      </c>
-      <c r="K231" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Заявка в статусе «Отменена»</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>Комментарий: «Клиент уже обслуживается, данные совпали с АБС»</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 8</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>Проверить блок «Внимание» на форме заявки</t>
-        </is>
-      </c>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>Выводится уведомление «Возможен дубль клиента. Проверьте данные в АБС перед подтверждением.» и данные найденного клиента: Рябова Дарья Сергеевна, 21.11.1992, паспорт 4514 600601</t>
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>900901</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>РТ_ЕФР -&gt; Общие шаги</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Вход в ЕФР в роли менеджера-операциониста</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>Готов</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>3/11/2025 09:40:12</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>В поле «Комментарий» ввести причину и нажать «Отменить операцию»</t>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Отменена»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>Комментарий: «Клиент уже обслуживается, данные совпали с АБС»</t>
+          <t>tst_oper01</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>900901</t>
+          <t>900902</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5576,7 +5601,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Вход в ЕФР в роли менеджера-операциониста</t>
+          <t>Вход в ЕФР в роли финансового консультанта</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -5596,7 +5621,7 @@
       </c>
       <c r="O234" s="2" t="inlineStr">
         <is>
-          <t>3/11/2025 09:40:12</t>
+          <t>3/11/2025 09:44:37</t>
         </is>
       </c>
       <c r="P234" s="2" t="inlineStr">
@@ -5613,7 +5638,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
@@ -5623,14 +5648,14 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>tst_oper01</t>
+          <t>tst_fk01</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>900902</t>
+          <t>900903</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -5640,7 +5665,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Вход в ЕФР в роли финансового консультанта</t>
+          <t>Вход в ЕФР в роли клиентского менеджера</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -5660,7 +5685,7 @@
       </c>
       <c r="O236" s="2" t="inlineStr">
         <is>
-          <t>3/11/2025 09:44:37</t>
+          <t>3/11/2025 09:47:05</t>
         </is>
       </c>
       <c r="P236" s="2" t="inlineStr">
@@ -5677,7 +5702,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
@@ -5687,14 +5712,14 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>tst_fk01</t>
+          <t>tst_kmtp01</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>900903</t>
+          <t>900904</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -5704,7 +5729,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Вход в ЕФР в роли клиентского менеджера</t>
+          <t>Вход в роли контролёра</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -5724,7 +5749,7 @@
       </c>
       <c r="O238" s="2" t="inlineStr">
         <is>
-          <t>3/11/2025 09:47:05</t>
+          <t>3/11/2025 09:52:19</t>
         </is>
       </c>
       <c r="P238" s="2" t="inlineStr">
@@ -5741,24 +5766,24 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>tst_kmtp01</t>
+          <t>tst_contr01</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>900904</t>
+          <t>900905</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -5768,7 +5793,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Вход в роли контролёра</t>
+          <t>Поиск клиента по паспорту</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -5788,12 +5813,12 @@
       </c>
       <c r="O240" s="2" t="inlineStr">
         <is>
-          <t>3/11/2025 09:52:19</t>
+          <t>3/12/2025 14:05:51</t>
         </is>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>Максим Гаврилин</t>
+          <t>Людмила Жаркова</t>
         </is>
       </c>
     </row>
@@ -5805,24 +5830,19 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J241" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>900905</t>
+          <t>900906</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -5832,7 +5852,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Поиск клиента по паспорту</t>
+          <t>Выход из ЕФР</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -5852,7 +5872,7 @@
       </c>
       <c r="O242" s="2" t="inlineStr">
         <is>
-          <t>3/12/2025 14:05:51</t>
+          <t>3/12/2025 14:11:26</t>
         </is>
       </c>
       <c r="P242" s="2" t="inlineStr">
@@ -5869,19 +5889,19 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>900906</t>
+          <t>900907</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -5891,7 +5911,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Выход из ЕФР</t>
+          <t>Открытие заявки контролёром</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -5911,12 +5931,12 @@
       </c>
       <c r="O244" s="2" t="inlineStr">
         <is>
-          <t>3/12/2025 14:11:26</t>
+          <t>8/04/2025 12:41:12</t>
         </is>
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>Людмила Жаркова</t>
+          <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
@@ -5928,81 +5948,22 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
-        </is>
-      </c>
-      <c r="I245" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница входа в ЕФР</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>900907</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>РТ_ЕФР -&gt; Общие шаги</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>Открытие заявки контролёром</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="M246" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="N246" s="2" t="inlineStr">
-        <is>
-          <t>Готов</t>
-        </is>
-      </c>
-      <c r="O246" s="2" t="inlineStr">
-        <is>
-          <t>8/04/2025 12:41:12</t>
-        </is>
-      </c>
-      <c r="P246" s="2" t="inlineStr">
-        <is>
-          <t>Максим Гаврилин</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="E247" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G247" s="2" t="inlineStr">
-        <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Шаг 2</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr">
         <is>
           <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
         <is>
           <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>
